--- a/read-me/ig/CdaTELToContactPointConceptMap.xlsx
+++ b/read-me/ig/CdaTELToContactPointConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:13:58+00:00</t>
+    <t>2026-07-17T08:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/read-me/ig/CdaTELToContactPointConceptMap.xlsx
+++ b/read-me/ig/CdaTELToContactPointConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:16:38+00:00</t>
+    <t>2026-07-17T12:13:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
